--- a/演示/吧唧排表示例.xlsx
+++ b/演示/吧唧排表示例.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RenSheet\演示\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFEBF131-596E-4F7B-B15B-CC0742534B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D915C04-8D2F-435E-9CD9-E59E3EFBF2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9270" yWindow="60" windowWidth="14420" windowHeight="15220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="22">
   <si>
     <t/>
   </si>
@@ -93,6 +93,10 @@
   </si>
   <si>
     <t>伊佐那</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>立牌</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -638,7 +642,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>

--- a/演示/吧唧排表示例.xlsx
+++ b/演示/吧唧排表示例.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RenSheet\演示\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D915C04-8D2F-435E-9CD9-E59E3EFBF2A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9BA7DE-0D51-4450-AF57-626D21EE24DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="21">
   <si>
     <t/>
   </si>
@@ -80,14 +80,6 @@
     <t>小丁</t>
   </si>
   <si>
-    <t>武道</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>麦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>三途</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -97,6 +89,10 @@
   </si>
   <si>
     <t>立牌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武道</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -642,7 +638,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -662,24 +658,21 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
-      </c>
-      <c r="B3">
-        <v>28</v>
       </c>
       <c r="C3">
         <v>22</v>

--- a/演示/吧唧排表示例.xlsx
+++ b/演示/吧唧排表示例.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RenSheet\演示\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F9BA7DE-0D51-4450-AF57-626D21EE24DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B26B8980-09B4-4945-BEA1-E7E82BD0FF74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3300" yWindow="60" windowWidth="14420" windowHeight="15220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2591" uniqueCount="272">
   <si>
     <t/>
   </si>
@@ -80,20 +80,772 @@
     <t>小丁</t>
   </si>
   <si>
-    <t>三途</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>伊佐那</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>立牌</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>武道</t>
+    <t>武道1</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武道2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>武道3</t>
+  </si>
+  <si>
+    <t>武道4</t>
+  </si>
+  <si>
+    <t>武道5</t>
+  </si>
+  <si>
+    <t>武道6</t>
+  </si>
+  <si>
+    <t>武道7</t>
+  </si>
+  <si>
+    <t>武道8</t>
+  </si>
+  <si>
+    <t>武道9</t>
+  </si>
+  <si>
+    <t>武道10</t>
+  </si>
+  <si>
+    <t>武道11</t>
+  </si>
+  <si>
+    <t>武道12</t>
+  </si>
+  <si>
+    <t>武道13</t>
+  </si>
+  <si>
+    <t>武道14</t>
+  </si>
+  <si>
+    <t>武道15</t>
+  </si>
+  <si>
+    <t>武道16</t>
+  </si>
+  <si>
+    <t>武道17</t>
+  </si>
+  <si>
+    <t>武道18</t>
+  </si>
+  <si>
+    <t>武道19</t>
+  </si>
+  <si>
+    <t>武道20</t>
+  </si>
+  <si>
+    <t>武道21</t>
+  </si>
+  <si>
+    <t>武道22</t>
+  </si>
+  <si>
+    <t>武道23</t>
+  </si>
+  <si>
+    <t>武道24</t>
+  </si>
+  <si>
+    <t>武道25</t>
+  </si>
+  <si>
+    <t>武道26</t>
+  </si>
+  <si>
+    <t>武道27</t>
+  </si>
+  <si>
+    <t>武道28</t>
+  </si>
+  <si>
+    <t>武道29</t>
+  </si>
+  <si>
+    <t>武道30</t>
+  </si>
+  <si>
+    <t>武道31</t>
+  </si>
+  <si>
+    <t>武道32</t>
+  </si>
+  <si>
+    <t>武道33</t>
+  </si>
+  <si>
+    <t>武道34</t>
+  </si>
+  <si>
+    <t>武道35</t>
+  </si>
+  <si>
+    <t>武道36</t>
+  </si>
+  <si>
+    <t>武道37</t>
+  </si>
+  <si>
+    <t>武道38</t>
+  </si>
+  <si>
+    <t>武道39</t>
+  </si>
+  <si>
+    <t>武道40</t>
+  </si>
+  <si>
+    <t>武道41</t>
+  </si>
+  <si>
+    <t>武道42</t>
+  </si>
+  <si>
+    <t>武道43</t>
+  </si>
+  <si>
+    <t>武道44</t>
+  </si>
+  <si>
+    <t>武道45</t>
+  </si>
+  <si>
+    <t>武道46</t>
+  </si>
+  <si>
+    <t>武道47</t>
+  </si>
+  <si>
+    <t>武道48</t>
+  </si>
+  <si>
+    <t>武道49</t>
+  </si>
+  <si>
+    <t>武道50</t>
+  </si>
+  <si>
+    <t>武道51</t>
+  </si>
+  <si>
+    <t>武道52</t>
+  </si>
+  <si>
+    <t>武道53</t>
+  </si>
+  <si>
+    <t>武道54</t>
+  </si>
+  <si>
+    <t>武道55</t>
+  </si>
+  <si>
+    <t>武道56</t>
+  </si>
+  <si>
+    <t>武道57</t>
+  </si>
+  <si>
+    <t>武道58</t>
+  </si>
+  <si>
+    <t>武道59</t>
+  </si>
+  <si>
+    <t>武道60</t>
+  </si>
+  <si>
+    <t>武道61</t>
+  </si>
+  <si>
+    <t>武道62</t>
+  </si>
+  <si>
+    <t>武道63</t>
+  </si>
+  <si>
+    <t>武道64</t>
+  </si>
+  <si>
+    <t>武道65</t>
+  </si>
+  <si>
+    <t>武道66</t>
+  </si>
+  <si>
+    <t>武道67</t>
+  </si>
+  <si>
+    <t>武道68</t>
+  </si>
+  <si>
+    <t>武道69</t>
+  </si>
+  <si>
+    <t>武道70</t>
+  </si>
+  <si>
+    <t>武道71</t>
+  </si>
+  <si>
+    <t>武道72</t>
+  </si>
+  <si>
+    <t>武道73</t>
+  </si>
+  <si>
+    <t>武道74</t>
+  </si>
+  <si>
+    <t>武道75</t>
+  </si>
+  <si>
+    <t>武道76</t>
+  </si>
+  <si>
+    <t>武道77</t>
+  </si>
+  <si>
+    <t>武道78</t>
+  </si>
+  <si>
+    <t>武道79</t>
+  </si>
+  <si>
+    <t>武道80</t>
+  </si>
+  <si>
+    <t>武道81</t>
+  </si>
+  <si>
+    <t>武道82</t>
+  </si>
+  <si>
+    <t>武道83</t>
+  </si>
+  <si>
+    <t>武道84</t>
+  </si>
+  <si>
+    <t>武道85</t>
+  </si>
+  <si>
+    <t>武道86</t>
+  </si>
+  <si>
+    <t>武道87</t>
+  </si>
+  <si>
+    <t>武道88</t>
+  </si>
+  <si>
+    <t>武道89</t>
+  </si>
+  <si>
+    <t>武道90</t>
+  </si>
+  <si>
+    <t>武道91</t>
+  </si>
+  <si>
+    <t>武道92</t>
+  </si>
+  <si>
+    <t>武道93</t>
+  </si>
+  <si>
+    <t>武道94</t>
+  </si>
+  <si>
+    <t>武道95</t>
+  </si>
+  <si>
+    <t>武道96</t>
+  </si>
+  <si>
+    <t>武道97</t>
+  </si>
+  <si>
+    <t>武道98</t>
+  </si>
+  <si>
+    <t>武道99</t>
+  </si>
+  <si>
+    <t>武道100</t>
+  </si>
+  <si>
+    <t>武道101</t>
+  </si>
+  <si>
+    <t>武道102</t>
+  </si>
+  <si>
+    <t>武道103</t>
+  </si>
+  <si>
+    <t>武道104</t>
+  </si>
+  <si>
+    <t>武道105</t>
+  </si>
+  <si>
+    <t>武道106</t>
+  </si>
+  <si>
+    <t>武道107</t>
+  </si>
+  <si>
+    <t>武道108</t>
+  </si>
+  <si>
+    <t>武道109</t>
+  </si>
+  <si>
+    <t>武道110</t>
+  </si>
+  <si>
+    <t>武道111</t>
+  </si>
+  <si>
+    <t>武道112</t>
+  </si>
+  <si>
+    <t>武道113</t>
+  </si>
+  <si>
+    <t>武道114</t>
+  </si>
+  <si>
+    <t>武道115</t>
+  </si>
+  <si>
+    <t>武道116</t>
+  </si>
+  <si>
+    <t>武道117</t>
+  </si>
+  <si>
+    <t>武道118</t>
+  </si>
+  <si>
+    <t>武道119</t>
+  </si>
+  <si>
+    <t>武道120</t>
+  </si>
+  <si>
+    <t>武道121</t>
+  </si>
+  <si>
+    <t>武道122</t>
+  </si>
+  <si>
+    <t>武道123</t>
+  </si>
+  <si>
+    <t>武道124</t>
+  </si>
+  <si>
+    <t>武道125</t>
+  </si>
+  <si>
+    <t>武道126</t>
+  </si>
+  <si>
+    <t>武道127</t>
+  </si>
+  <si>
+    <t>武道128</t>
+  </si>
+  <si>
+    <t>武道129</t>
+  </si>
+  <si>
+    <t>武道130</t>
+  </si>
+  <si>
+    <t>武道131</t>
+  </si>
+  <si>
+    <t>武道132</t>
+  </si>
+  <si>
+    <t>武道133</t>
+  </si>
+  <si>
+    <t>武道134</t>
+  </si>
+  <si>
+    <t>武道135</t>
+  </si>
+  <si>
+    <t>武道136</t>
+  </si>
+  <si>
+    <t>武道137</t>
+  </si>
+  <si>
+    <t>武道138</t>
+  </si>
+  <si>
+    <t>武道139</t>
+  </si>
+  <si>
+    <t>武道140</t>
+  </si>
+  <si>
+    <t>武道141</t>
+  </si>
+  <si>
+    <t>武道142</t>
+  </si>
+  <si>
+    <t>武道143</t>
+  </si>
+  <si>
+    <t>武道144</t>
+  </si>
+  <si>
+    <t>武道145</t>
+  </si>
+  <si>
+    <t>武道146</t>
+  </si>
+  <si>
+    <t>武道147</t>
+  </si>
+  <si>
+    <t>武道148</t>
+  </si>
+  <si>
+    <t>武道149</t>
+  </si>
+  <si>
+    <t>武道150</t>
+  </si>
+  <si>
+    <t>武道151</t>
+  </si>
+  <si>
+    <t>武道152</t>
+  </si>
+  <si>
+    <t>武道153</t>
+  </si>
+  <si>
+    <t>武道154</t>
+  </si>
+  <si>
+    <t>武道155</t>
+  </si>
+  <si>
+    <t>武道156</t>
+  </si>
+  <si>
+    <t>武道157</t>
+  </si>
+  <si>
+    <t>武道158</t>
+  </si>
+  <si>
+    <t>武道159</t>
+  </si>
+  <si>
+    <t>武道160</t>
+  </si>
+  <si>
+    <t>武道161</t>
+  </si>
+  <si>
+    <t>武道162</t>
+  </si>
+  <si>
+    <t>武道163</t>
+  </si>
+  <si>
+    <t>武道164</t>
+  </si>
+  <si>
+    <t>武道165</t>
+  </si>
+  <si>
+    <t>武道166</t>
+  </si>
+  <si>
+    <t>武道167</t>
+  </si>
+  <si>
+    <t>武道168</t>
+  </si>
+  <si>
+    <t>武道169</t>
+  </si>
+  <si>
+    <t>武道170</t>
+  </si>
+  <si>
+    <t>武道171</t>
+  </si>
+  <si>
+    <t>武道172</t>
+  </si>
+  <si>
+    <t>武道173</t>
+  </si>
+  <si>
+    <t>武道174</t>
+  </si>
+  <si>
+    <t>武道175</t>
+  </si>
+  <si>
+    <t>武道176</t>
+  </si>
+  <si>
+    <t>武道177</t>
+  </si>
+  <si>
+    <t>武道178</t>
+  </si>
+  <si>
+    <t>武道179</t>
+  </si>
+  <si>
+    <t>武道180</t>
+  </si>
+  <si>
+    <t>武道181</t>
+  </si>
+  <si>
+    <t>武道182</t>
+  </si>
+  <si>
+    <t>武道183</t>
+  </si>
+  <si>
+    <t>武道184</t>
+  </si>
+  <si>
+    <t>武道185</t>
+  </si>
+  <si>
+    <t>武道186</t>
+  </si>
+  <si>
+    <t>武道187</t>
+  </si>
+  <si>
+    <t>武道188</t>
+  </si>
+  <si>
+    <t>武道189</t>
+  </si>
+  <si>
+    <t>武道190</t>
+  </si>
+  <si>
+    <t>武道191</t>
+  </si>
+  <si>
+    <t>武道192</t>
+  </si>
+  <si>
+    <t>武道193</t>
+  </si>
+  <si>
+    <t>武道194</t>
+  </si>
+  <si>
+    <t>武道195</t>
+  </si>
+  <si>
+    <t>武道196</t>
+  </si>
+  <si>
+    <t>武道197</t>
+  </si>
+  <si>
+    <t>武道198</t>
+  </si>
+  <si>
+    <t>武道199</t>
+  </si>
+  <si>
+    <t>武道200</t>
+  </si>
+  <si>
+    <t>武道201</t>
+  </si>
+  <si>
+    <t>武道202</t>
+  </si>
+  <si>
+    <t>武道203</t>
+  </si>
+  <si>
+    <t>武道204</t>
+  </si>
+  <si>
+    <t>武道205</t>
+  </si>
+  <si>
+    <t>武道206</t>
+  </si>
+  <si>
+    <t>武道207</t>
+  </si>
+  <si>
+    <t>武道208</t>
+  </si>
+  <si>
+    <t>武道209</t>
+  </si>
+  <si>
+    <t>武道210</t>
+  </si>
+  <si>
+    <t>武道211</t>
+  </si>
+  <si>
+    <t>武道212</t>
+  </si>
+  <si>
+    <t>武道213</t>
+  </si>
+  <si>
+    <t>武道214</t>
+  </si>
+  <si>
+    <t>武道215</t>
+  </si>
+  <si>
+    <t>武道216</t>
+  </si>
+  <si>
+    <t>武道217</t>
+  </si>
+  <si>
+    <t>武道218</t>
+  </si>
+  <si>
+    <t>武道219</t>
+  </si>
+  <si>
+    <t>武道220</t>
+  </si>
+  <si>
+    <t>武道221</t>
+  </si>
+  <si>
+    <t>武道222</t>
+  </si>
+  <si>
+    <t>武道223</t>
+  </si>
+  <si>
+    <t>武道224</t>
+  </si>
+  <si>
+    <t>武道225</t>
+  </si>
+  <si>
+    <t>武道226</t>
+  </si>
+  <si>
+    <t>武道227</t>
+  </si>
+  <si>
+    <t>武道228</t>
+  </si>
+  <si>
+    <t>武道229</t>
+  </si>
+  <si>
+    <t>武道230</t>
+  </si>
+  <si>
+    <t>武道231</t>
+  </si>
+  <si>
+    <t>武道232</t>
+  </si>
+  <si>
+    <t>武道233</t>
+  </si>
+  <si>
+    <t>武道234</t>
+  </si>
+  <si>
+    <t>武道235</t>
+  </si>
+  <si>
+    <t>武道236</t>
+  </si>
+  <si>
+    <t>武道237</t>
+  </si>
+  <si>
+    <t>武道238</t>
+  </si>
+  <si>
+    <t>武道239</t>
+  </si>
+  <si>
+    <t>武道240</t>
+  </si>
+  <si>
+    <t>武道241</t>
+  </si>
+  <si>
+    <t>武道242</t>
+  </si>
+  <si>
+    <t>武道243</t>
+  </si>
+  <si>
+    <t>武道244</t>
+  </si>
+  <si>
+    <t>武道245</t>
+  </si>
+  <si>
+    <t>武道246</t>
+  </si>
+  <si>
+    <t>武道247</t>
+  </si>
+  <si>
+    <t>武道248</t>
+  </si>
+  <si>
+    <t>武道249</t>
+  </si>
+  <si>
+    <t>武道250</t>
+  </si>
+  <si>
+    <t>武道251</t>
+  </si>
+  <si>
+    <t>武道252</t>
+  </si>
+  <si>
+    <t>武道253</t>
+  </si>
+  <si>
+    <t>武道254</t>
   </si>
 </sst>
 </file>
@@ -460,16 +1212,16 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>24</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -633,58 +1385,1552 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F588E5AB-8579-4873-93BE-D78C5595A53C}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:IU12"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:255" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" t="s">
-        <v>0</v>
-      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:255" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" t="s">
+        <v>25</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M2" t="s">
+        <v>29</v>
+      </c>
+      <c r="N2" t="s">
+        <v>30</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S2" t="s">
+        <v>35</v>
+      </c>
+      <c r="T2" t="s">
+        <v>36</v>
+      </c>
+      <c r="U2" t="s">
+        <v>37</v>
+      </c>
+      <c r="V2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W2" t="s">
+        <v>39</v>
+      </c>
+      <c r="X2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>47</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>52</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>53</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>57</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AQ2" t="s">
+        <v>59</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>60</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>61</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>62</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>63</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>65</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>66</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>68</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>69</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>70</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>71</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>72</v>
+      </c>
+      <c r="BE2" t="s">
+        <v>73</v>
+      </c>
+      <c r="BF2" t="s">
+        <v>74</v>
+      </c>
+      <c r="BG2" t="s">
+        <v>75</v>
+      </c>
+      <c r="BH2" t="s">
+        <v>76</v>
+      </c>
+      <c r="BI2" t="s">
+        <v>77</v>
+      </c>
+      <c r="BJ2" t="s">
+        <v>78</v>
+      </c>
+      <c r="BK2" t="s">
+        <v>79</v>
+      </c>
+      <c r="BL2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BM2" t="s">
+        <v>81</v>
+      </c>
+      <c r="BN2" t="s">
+        <v>82</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>83</v>
+      </c>
+      <c r="BP2" t="s">
+        <v>84</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>85</v>
+      </c>
+      <c r="BR2" t="s">
+        <v>86</v>
+      </c>
+      <c r="BS2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>88</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>89</v>
+      </c>
+      <c r="BV2" t="s">
+        <v>90</v>
+      </c>
+      <c r="BW2" t="s">
+        <v>91</v>
+      </c>
+      <c r="BX2" t="s">
+        <v>92</v>
+      </c>
+      <c r="BY2" t="s">
+        <v>93</v>
+      </c>
+      <c r="BZ2" t="s">
+        <v>94</v>
+      </c>
+      <c r="CA2" t="s">
+        <v>95</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>96</v>
+      </c>
+      <c r="CC2" t="s">
+        <v>97</v>
+      </c>
+      <c r="CD2" t="s">
+        <v>98</v>
+      </c>
+      <c r="CE2" t="s">
+        <v>99</v>
+      </c>
+      <c r="CF2" t="s">
+        <v>100</v>
+      </c>
+      <c r="CG2" t="s">
+        <v>101</v>
+      </c>
+      <c r="CH2" t="s">
+        <v>102</v>
+      </c>
+      <c r="CI2" t="s">
+        <v>103</v>
+      </c>
+      <c r="CJ2" t="s">
+        <v>104</v>
+      </c>
+      <c r="CK2" t="s">
+        <v>105</v>
+      </c>
+      <c r="CL2" t="s">
+        <v>106</v>
+      </c>
+      <c r="CM2" t="s">
+        <v>107</v>
+      </c>
+      <c r="CN2" t="s">
+        <v>108</v>
+      </c>
+      <c r="CO2" t="s">
+        <v>109</v>
+      </c>
+      <c r="CP2" t="s">
+        <v>110</v>
+      </c>
+      <c r="CQ2" t="s">
+        <v>111</v>
+      </c>
+      <c r="CR2" t="s">
+        <v>112</v>
+      </c>
+      <c r="CS2" t="s">
+        <v>113</v>
+      </c>
+      <c r="CT2" t="s">
+        <v>114</v>
+      </c>
+      <c r="CU2" t="s">
+        <v>115</v>
+      </c>
+      <c r="CV2" t="s">
+        <v>116</v>
+      </c>
+      <c r="CW2" t="s">
+        <v>117</v>
+      </c>
+      <c r="CX2" t="s">
+        <v>118</v>
+      </c>
+      <c r="CY2" t="s">
+        <v>119</v>
+      </c>
+      <c r="CZ2" t="s">
+        <v>120</v>
+      </c>
+      <c r="DA2" t="s">
+        <v>121</v>
+      </c>
+      <c r="DB2" t="s">
+        <v>122</v>
+      </c>
+      <c r="DC2" t="s">
+        <v>123</v>
+      </c>
+      <c r="DD2" t="s">
+        <v>124</v>
+      </c>
+      <c r="DE2" t="s">
+        <v>125</v>
+      </c>
+      <c r="DF2" t="s">
+        <v>126</v>
+      </c>
+      <c r="DG2" t="s">
+        <v>127</v>
+      </c>
+      <c r="DH2" t="s">
+        <v>128</v>
+      </c>
+      <c r="DI2" t="s">
+        <v>129</v>
+      </c>
+      <c r="DJ2" t="s">
+        <v>130</v>
+      </c>
+      <c r="DK2" t="s">
+        <v>131</v>
+      </c>
+      <c r="DL2" t="s">
+        <v>132</v>
+      </c>
+      <c r="DM2" t="s">
+        <v>133</v>
+      </c>
+      <c r="DN2" t="s">
+        <v>134</v>
+      </c>
+      <c r="DO2" t="s">
+        <v>135</v>
+      </c>
+      <c r="DP2" t="s">
+        <v>136</v>
+      </c>
+      <c r="DQ2" t="s">
+        <v>137</v>
+      </c>
+      <c r="DR2" t="s">
+        <v>138</v>
+      </c>
+      <c r="DS2" t="s">
+        <v>139</v>
+      </c>
+      <c r="DT2" t="s">
+        <v>140</v>
+      </c>
+      <c r="DU2" t="s">
+        <v>141</v>
+      </c>
+      <c r="DV2" t="s">
+        <v>142</v>
+      </c>
+      <c r="DW2" t="s">
+        <v>143</v>
+      </c>
+      <c r="DX2" t="s">
+        <v>144</v>
+      </c>
+      <c r="DY2" t="s">
+        <v>145</v>
+      </c>
+      <c r="DZ2" t="s">
+        <v>146</v>
+      </c>
+      <c r="EA2" t="s">
+        <v>147</v>
+      </c>
+      <c r="EB2" t="s">
+        <v>148</v>
+      </c>
+      <c r="EC2" t="s">
+        <v>149</v>
+      </c>
+      <c r="ED2" t="s">
+        <v>150</v>
+      </c>
+      <c r="EE2" t="s">
+        <v>151</v>
+      </c>
+      <c r="EF2" t="s">
+        <v>152</v>
+      </c>
+      <c r="EG2" t="s">
+        <v>153</v>
+      </c>
+      <c r="EH2" t="s">
+        <v>154</v>
+      </c>
+      <c r="EI2" t="s">
+        <v>155</v>
+      </c>
+      <c r="EJ2" t="s">
+        <v>156</v>
+      </c>
+      <c r="EK2" t="s">
+        <v>157</v>
+      </c>
+      <c r="EL2" t="s">
+        <v>158</v>
+      </c>
+      <c r="EM2" t="s">
+        <v>159</v>
+      </c>
+      <c r="EN2" t="s">
+        <v>160</v>
+      </c>
+      <c r="EO2" t="s">
+        <v>161</v>
+      </c>
+      <c r="EP2" t="s">
+        <v>162</v>
+      </c>
+      <c r="EQ2" t="s">
+        <v>163</v>
+      </c>
+      <c r="ER2" t="s">
+        <v>164</v>
+      </c>
+      <c r="ES2" t="s">
+        <v>165</v>
+      </c>
+      <c r="ET2" t="s">
+        <v>166</v>
+      </c>
+      <c r="EU2" t="s">
+        <v>167</v>
+      </c>
+      <c r="EV2" t="s">
+        <v>168</v>
+      </c>
+      <c r="EW2" t="s">
+        <v>169</v>
+      </c>
+      <c r="EX2" t="s">
+        <v>170</v>
+      </c>
+      <c r="EY2" t="s">
+        <v>171</v>
+      </c>
+      <c r="EZ2" t="s">
+        <v>172</v>
+      </c>
+      <c r="FA2" t="s">
+        <v>173</v>
+      </c>
+      <c r="FB2" t="s">
+        <v>174</v>
+      </c>
+      <c r="FC2" t="s">
+        <v>175</v>
+      </c>
+      <c r="FD2" t="s">
+        <v>176</v>
+      </c>
+      <c r="FE2" t="s">
+        <v>177</v>
+      </c>
+      <c r="FF2" t="s">
+        <v>178</v>
+      </c>
+      <c r="FG2" t="s">
+        <v>179</v>
+      </c>
+      <c r="FH2" t="s">
+        <v>180</v>
+      </c>
+      <c r="FI2" t="s">
+        <v>181</v>
+      </c>
+      <c r="FJ2" t="s">
+        <v>182</v>
+      </c>
+      <c r="FK2" t="s">
+        <v>183</v>
+      </c>
+      <c r="FL2" t="s">
+        <v>184</v>
+      </c>
+      <c r="FM2" t="s">
+        <v>185</v>
+      </c>
+      <c r="FN2" t="s">
+        <v>186</v>
+      </c>
+      <c r="FO2" t="s">
+        <v>187</v>
+      </c>
+      <c r="FP2" t="s">
+        <v>188</v>
+      </c>
+      <c r="FQ2" t="s">
+        <v>189</v>
+      </c>
+      <c r="FR2" t="s">
+        <v>190</v>
+      </c>
+      <c r="FS2" t="s">
+        <v>191</v>
+      </c>
+      <c r="FT2" t="s">
+        <v>192</v>
+      </c>
+      <c r="FU2" t="s">
+        <v>193</v>
+      </c>
+      <c r="FV2" t="s">
+        <v>194</v>
+      </c>
+      <c r="FW2" t="s">
+        <v>195</v>
+      </c>
+      <c r="FX2" t="s">
+        <v>196</v>
+      </c>
+      <c r="FY2" t="s">
+        <v>197</v>
+      </c>
+      <c r="FZ2" t="s">
+        <v>198</v>
+      </c>
+      <c r="GA2" t="s">
+        <v>199</v>
+      </c>
+      <c r="GB2" t="s">
+        <v>200</v>
+      </c>
+      <c r="GC2" t="s">
+        <v>201</v>
+      </c>
+      <c r="GD2" t="s">
+        <v>202</v>
+      </c>
+      <c r="GE2" t="s">
+        <v>203</v>
+      </c>
+      <c r="GF2" t="s">
+        <v>204</v>
+      </c>
+      <c r="GG2" t="s">
+        <v>205</v>
+      </c>
+      <c r="GH2" t="s">
+        <v>206</v>
+      </c>
+      <c r="GI2" t="s">
+        <v>207</v>
+      </c>
+      <c r="GJ2" t="s">
+        <v>208</v>
+      </c>
+      <c r="GK2" t="s">
+        <v>209</v>
+      </c>
+      <c r="GL2" t="s">
+        <v>210</v>
+      </c>
+      <c r="GM2" t="s">
+        <v>211</v>
+      </c>
+      <c r="GN2" t="s">
+        <v>212</v>
+      </c>
+      <c r="GO2" t="s">
+        <v>213</v>
+      </c>
+      <c r="GP2" t="s">
+        <v>214</v>
+      </c>
+      <c r="GQ2" t="s">
+        <v>215</v>
+      </c>
+      <c r="GR2" t="s">
+        <v>216</v>
+      </c>
+      <c r="GS2" t="s">
+        <v>217</v>
+      </c>
+      <c r="GT2" t="s">
+        <v>218</v>
+      </c>
+      <c r="GU2" t="s">
+        <v>219</v>
+      </c>
+      <c r="GV2" t="s">
+        <v>220</v>
+      </c>
+      <c r="GW2" t="s">
+        <v>221</v>
+      </c>
+      <c r="GX2" t="s">
+        <v>222</v>
+      </c>
+      <c r="GY2" t="s">
+        <v>223</v>
+      </c>
+      <c r="GZ2" t="s">
+        <v>224</v>
+      </c>
+      <c r="HA2" t="s">
+        <v>225</v>
+      </c>
+      <c r="HB2" t="s">
+        <v>226</v>
+      </c>
+      <c r="HC2" t="s">
+        <v>227</v>
+      </c>
+      <c r="HD2" t="s">
+        <v>228</v>
+      </c>
+      <c r="HE2" t="s">
+        <v>229</v>
+      </c>
+      <c r="HF2" t="s">
+        <v>230</v>
+      </c>
+      <c r="HG2" t="s">
+        <v>231</v>
+      </c>
+      <c r="HH2" t="s">
+        <v>232</v>
+      </c>
+      <c r="HI2" t="s">
+        <v>233</v>
+      </c>
+      <c r="HJ2" t="s">
+        <v>234</v>
+      </c>
+      <c r="HK2" t="s">
+        <v>235</v>
+      </c>
+      <c r="HL2" t="s">
+        <v>236</v>
+      </c>
+      <c r="HM2" t="s">
+        <v>237</v>
+      </c>
+      <c r="HN2" t="s">
+        <v>238</v>
+      </c>
+      <c r="HO2" t="s">
+        <v>239</v>
+      </c>
+      <c r="HP2" t="s">
+        <v>240</v>
+      </c>
+      <c r="HQ2" t="s">
+        <v>241</v>
+      </c>
+      <c r="HR2" t="s">
+        <v>242</v>
+      </c>
+      <c r="HS2" t="s">
+        <v>243</v>
+      </c>
+      <c r="HT2" t="s">
+        <v>244</v>
+      </c>
+      <c r="HU2" t="s">
+        <v>245</v>
+      </c>
+      <c r="HV2" t="s">
+        <v>246</v>
+      </c>
+      <c r="HW2" t="s">
+        <v>247</v>
+      </c>
+      <c r="HX2" t="s">
+        <v>248</v>
+      </c>
+      <c r="HY2" t="s">
+        <v>249</v>
+      </c>
+      <c r="HZ2" t="s">
+        <v>250</v>
+      </c>
+      <c r="IA2" t="s">
+        <v>251</v>
+      </c>
+      <c r="IB2" t="s">
+        <v>252</v>
+      </c>
+      <c r="IC2" t="s">
+        <v>253</v>
+      </c>
+      <c r="ID2" t="s">
+        <v>254</v>
+      </c>
+      <c r="IE2" t="s">
+        <v>255</v>
+      </c>
+      <c r="IF2" t="s">
+        <v>256</v>
+      </c>
+      <c r="IG2" t="s">
+        <v>257</v>
+      </c>
+      <c r="IH2" t="s">
+        <v>258</v>
+      </c>
+      <c r="II2" t="s">
+        <v>259</v>
+      </c>
+      <c r="IJ2" t="s">
+        <v>260</v>
+      </c>
+      <c r="IK2" t="s">
+        <v>261</v>
+      </c>
+      <c r="IL2" t="s">
+        <v>262</v>
+      </c>
+      <c r="IM2" t="s">
+        <v>263</v>
+      </c>
+      <c r="IN2" t="s">
+        <v>264</v>
+      </c>
+      <c r="IO2" t="s">
+        <v>265</v>
+      </c>
+      <c r="IP2" t="s">
+        <v>266</v>
+      </c>
+      <c r="IQ2" t="s">
+        <v>267</v>
+      </c>
+      <c r="IR2" t="s">
+        <v>268</v>
+      </c>
+      <c r="IS2" t="s">
+        <v>269</v>
+      </c>
+      <c r="IT2" t="s">
+        <v>270</v>
+      </c>
+      <c r="IU2" t="s">
+        <v>271</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:255" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
       <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3">
+        <v>5</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>7</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>9</v>
+      </c>
+      <c r="I3">
+        <v>10</v>
+      </c>
+      <c r="J3">
+        <v>11</v>
+      </c>
+      <c r="K3">
+        <v>12</v>
+      </c>
+      <c r="L3">
+        <v>13</v>
+      </c>
+      <c r="M3">
+        <v>14</v>
+      </c>
+      <c r="N3">
+        <v>15</v>
+      </c>
+      <c r="O3">
+        <v>16</v>
+      </c>
+      <c r="P3">
+        <v>17</v>
+      </c>
+      <c r="Q3">
+        <v>18</v>
+      </c>
+      <c r="R3">
+        <v>19</v>
+      </c>
+      <c r="S3">
+        <v>20</v>
+      </c>
+      <c r="T3">
+        <v>21</v>
+      </c>
+      <c r="U3">
         <v>22</v>
       </c>
-      <c r="D3">
+      <c r="V3">
+        <v>23</v>
+      </c>
+      <c r="W3">
+        <v>24</v>
+      </c>
+      <c r="X3">
+        <v>25</v>
+      </c>
+      <c r="Y3">
         <v>26</v>
       </c>
-      <c r="E3">
-        <v>24</v>
+      <c r="Z3">
+        <v>27</v>
+      </c>
+      <c r="AA3">
+        <v>28</v>
+      </c>
+      <c r="AB3">
+        <v>29</v>
+      </c>
+      <c r="AC3">
+        <v>30</v>
+      </c>
+      <c r="AD3">
+        <v>31</v>
+      </c>
+      <c r="AE3">
+        <v>32</v>
+      </c>
+      <c r="AF3">
+        <v>33</v>
+      </c>
+      <c r="AG3">
+        <v>34</v>
+      </c>
+      <c r="AH3">
+        <v>35</v>
+      </c>
+      <c r="AI3">
+        <v>36</v>
+      </c>
+      <c r="AJ3">
+        <v>37</v>
+      </c>
+      <c r="AK3">
+        <v>38</v>
+      </c>
+      <c r="AL3">
+        <v>39</v>
+      </c>
+      <c r="AM3">
+        <v>40</v>
+      </c>
+      <c r="AN3">
+        <v>41</v>
+      </c>
+      <c r="AO3">
+        <v>42</v>
+      </c>
+      <c r="AP3">
+        <v>43</v>
+      </c>
+      <c r="AQ3">
+        <v>44</v>
+      </c>
+      <c r="AR3">
+        <v>45</v>
+      </c>
+      <c r="AS3">
+        <v>46</v>
+      </c>
+      <c r="AT3">
+        <v>47</v>
+      </c>
+      <c r="AU3">
+        <v>48</v>
+      </c>
+      <c r="AV3">
+        <v>49</v>
+      </c>
+      <c r="AW3">
+        <v>50</v>
+      </c>
+      <c r="AX3">
+        <v>51</v>
+      </c>
+      <c r="AY3">
+        <v>52</v>
+      </c>
+      <c r="AZ3">
+        <v>53</v>
+      </c>
+      <c r="BA3">
+        <v>54</v>
+      </c>
+      <c r="BB3">
+        <v>55</v>
+      </c>
+      <c r="BC3">
+        <v>56</v>
+      </c>
+      <c r="BD3">
+        <v>57</v>
+      </c>
+      <c r="BE3">
+        <v>58</v>
+      </c>
+      <c r="BF3">
+        <v>59</v>
+      </c>
+      <c r="BG3">
+        <v>60</v>
+      </c>
+      <c r="BH3">
+        <v>61</v>
+      </c>
+      <c r="BI3">
+        <v>62</v>
+      </c>
+      <c r="BJ3">
+        <v>63</v>
+      </c>
+      <c r="BK3">
+        <v>64</v>
+      </c>
+      <c r="BL3">
+        <v>65</v>
+      </c>
+      <c r="BM3">
+        <v>66</v>
+      </c>
+      <c r="BN3">
+        <v>67</v>
+      </c>
+      <c r="BO3">
+        <v>68</v>
+      </c>
+      <c r="BP3">
+        <v>69</v>
+      </c>
+      <c r="BQ3">
+        <v>70</v>
+      </c>
+      <c r="BR3">
+        <v>71</v>
+      </c>
+      <c r="BS3">
+        <v>72</v>
+      </c>
+      <c r="BT3">
+        <v>73</v>
+      </c>
+      <c r="BU3">
+        <v>74</v>
+      </c>
+      <c r="BV3">
+        <v>75</v>
+      </c>
+      <c r="BW3">
+        <v>76</v>
+      </c>
+      <c r="BX3">
+        <v>77</v>
+      </c>
+      <c r="BY3">
+        <v>78</v>
+      </c>
+      <c r="BZ3">
+        <v>79</v>
+      </c>
+      <c r="CA3">
+        <v>80</v>
+      </c>
+      <c r="CB3">
+        <v>81</v>
+      </c>
+      <c r="CC3">
+        <v>82</v>
+      </c>
+      <c r="CD3">
+        <v>83</v>
+      </c>
+      <c r="CE3">
+        <v>84</v>
+      </c>
+      <c r="CF3">
+        <v>85</v>
+      </c>
+      <c r="CG3">
+        <v>86</v>
+      </c>
+      <c r="CH3">
+        <v>87</v>
+      </c>
+      <c r="CI3">
+        <v>88</v>
+      </c>
+      <c r="CJ3">
+        <v>89</v>
+      </c>
+      <c r="CK3">
+        <v>90</v>
+      </c>
+      <c r="CL3">
+        <v>91</v>
+      </c>
+      <c r="CM3">
+        <v>92</v>
+      </c>
+      <c r="CN3">
+        <v>93</v>
+      </c>
+      <c r="CO3">
+        <v>94</v>
+      </c>
+      <c r="CP3">
+        <v>95</v>
+      </c>
+      <c r="CQ3">
+        <v>96</v>
+      </c>
+      <c r="CR3">
+        <v>97</v>
+      </c>
+      <c r="CS3">
+        <v>98</v>
+      </c>
+      <c r="CT3">
+        <v>99</v>
+      </c>
+      <c r="CU3">
+        <v>100</v>
+      </c>
+      <c r="CV3">
+        <v>101</v>
+      </c>
+      <c r="CW3">
+        <v>102</v>
+      </c>
+      <c r="CX3">
+        <v>103</v>
+      </c>
+      <c r="CY3">
+        <v>104</v>
+      </c>
+      <c r="CZ3">
+        <v>105</v>
+      </c>
+      <c r="DA3">
+        <v>106</v>
+      </c>
+      <c r="DB3">
+        <v>107</v>
+      </c>
+      <c r="DC3">
+        <v>108</v>
+      </c>
+      <c r="DD3">
+        <v>109</v>
+      </c>
+      <c r="DE3">
+        <v>110</v>
+      </c>
+      <c r="DF3">
+        <v>111</v>
+      </c>
+      <c r="DG3">
+        <v>112</v>
+      </c>
+      <c r="DH3">
+        <v>113</v>
+      </c>
+      <c r="DI3">
+        <v>114</v>
+      </c>
+      <c r="DJ3">
+        <v>115</v>
+      </c>
+      <c r="DK3">
+        <v>116</v>
+      </c>
+      <c r="DL3">
+        <v>117</v>
+      </c>
+      <c r="DM3">
+        <v>118</v>
+      </c>
+      <c r="DN3">
+        <v>119</v>
+      </c>
+      <c r="DO3">
+        <v>120</v>
+      </c>
+      <c r="DP3">
+        <v>121</v>
+      </c>
+      <c r="DQ3">
+        <v>122</v>
+      </c>
+      <c r="DR3">
+        <v>123</v>
+      </c>
+      <c r="DS3">
+        <v>124</v>
+      </c>
+      <c r="DT3">
+        <v>125</v>
+      </c>
+      <c r="DU3">
+        <v>126</v>
+      </c>
+      <c r="DV3">
+        <v>127</v>
+      </c>
+      <c r="DW3">
+        <v>128</v>
+      </c>
+      <c r="DX3">
+        <v>129</v>
+      </c>
+      <c r="DY3">
+        <v>130</v>
+      </c>
+      <c r="DZ3">
+        <v>131</v>
+      </c>
+      <c r="EA3">
+        <v>132</v>
+      </c>
+      <c r="EB3">
+        <v>133</v>
+      </c>
+      <c r="EC3">
+        <v>134</v>
+      </c>
+      <c r="ED3">
+        <v>135</v>
+      </c>
+      <c r="EE3">
+        <v>136</v>
+      </c>
+      <c r="EF3">
+        <v>137</v>
+      </c>
+      <c r="EG3">
+        <v>138</v>
+      </c>
+      <c r="EH3">
+        <v>139</v>
+      </c>
+      <c r="EI3">
+        <v>140</v>
+      </c>
+      <c r="EJ3">
+        <v>141</v>
+      </c>
+      <c r="EK3">
+        <v>142</v>
+      </c>
+      <c r="EL3">
+        <v>143</v>
+      </c>
+      <c r="EM3">
+        <v>144</v>
+      </c>
+      <c r="EN3">
+        <v>145</v>
+      </c>
+      <c r="EO3">
+        <v>146</v>
+      </c>
+      <c r="EP3">
+        <v>147</v>
+      </c>
+      <c r="EQ3">
+        <v>148</v>
+      </c>
+      <c r="ER3">
+        <v>149</v>
+      </c>
+      <c r="ES3">
+        <v>150</v>
+      </c>
+      <c r="ET3">
+        <v>151</v>
+      </c>
+      <c r="EU3">
+        <v>152</v>
+      </c>
+      <c r="EV3">
+        <v>153</v>
+      </c>
+      <c r="EW3">
+        <v>154</v>
+      </c>
+      <c r="EX3">
+        <v>155</v>
+      </c>
+      <c r="EY3">
+        <v>156</v>
+      </c>
+      <c r="EZ3">
+        <v>157</v>
+      </c>
+      <c r="FA3">
+        <v>158</v>
+      </c>
+      <c r="FB3">
+        <v>159</v>
+      </c>
+      <c r="FC3">
+        <v>160</v>
+      </c>
+      <c r="FD3">
+        <v>161</v>
+      </c>
+      <c r="FE3">
+        <v>162</v>
+      </c>
+      <c r="FF3">
+        <v>163</v>
+      </c>
+      <c r="FG3">
+        <v>164</v>
+      </c>
+      <c r="FH3">
+        <v>165</v>
+      </c>
+      <c r="FI3">
+        <v>166</v>
+      </c>
+      <c r="FJ3">
+        <v>167</v>
+      </c>
+      <c r="FK3">
+        <v>168</v>
+      </c>
+      <c r="FL3">
+        <v>169</v>
+      </c>
+      <c r="FM3">
+        <v>170</v>
+      </c>
+      <c r="FN3">
+        <v>171</v>
+      </c>
+      <c r="FO3">
+        <v>172</v>
+      </c>
+      <c r="FP3">
+        <v>173</v>
+      </c>
+      <c r="FQ3">
+        <v>174</v>
+      </c>
+      <c r="FR3">
+        <v>175</v>
+      </c>
+      <c r="FS3">
+        <v>176</v>
+      </c>
+      <c r="FT3">
+        <v>177</v>
+      </c>
+      <c r="FU3">
+        <v>178</v>
+      </c>
+      <c r="FV3">
+        <v>179</v>
+      </c>
+      <c r="FW3">
+        <v>180</v>
+      </c>
+      <c r="FX3">
+        <v>181</v>
+      </c>
+      <c r="FY3">
+        <v>182</v>
+      </c>
+      <c r="FZ3">
+        <v>183</v>
+      </c>
+      <c r="GA3">
+        <v>184</v>
+      </c>
+      <c r="GB3">
+        <v>185</v>
+      </c>
+      <c r="GC3">
+        <v>186</v>
+      </c>
+      <c r="GD3">
+        <v>187</v>
+      </c>
+      <c r="GE3">
+        <v>188</v>
+      </c>
+      <c r="GF3">
+        <v>189</v>
+      </c>
+      <c r="GG3">
+        <v>190</v>
+      </c>
+      <c r="GH3">
+        <v>191</v>
+      </c>
+      <c r="GI3">
+        <v>192</v>
+      </c>
+      <c r="GJ3">
+        <v>193</v>
+      </c>
+      <c r="GK3">
+        <v>194</v>
+      </c>
+      <c r="GL3">
+        <v>195</v>
+      </c>
+      <c r="GM3">
+        <v>196</v>
+      </c>
+      <c r="GN3">
+        <v>197</v>
+      </c>
+      <c r="GO3">
+        <v>198</v>
+      </c>
+      <c r="GP3">
+        <v>199</v>
+      </c>
+      <c r="GQ3">
+        <v>200</v>
+      </c>
+      <c r="GR3">
+        <v>201</v>
+      </c>
+      <c r="GS3">
+        <v>202</v>
+      </c>
+      <c r="GT3">
+        <v>203</v>
+      </c>
+      <c r="GU3">
+        <v>204</v>
+      </c>
+      <c r="GV3">
+        <v>205</v>
+      </c>
+      <c r="GW3">
+        <v>206</v>
+      </c>
+      <c r="GX3">
+        <v>207</v>
+      </c>
+      <c r="GY3">
+        <v>208</v>
+      </c>
+      <c r="GZ3">
+        <v>209</v>
+      </c>
+      <c r="HA3">
+        <v>210</v>
+      </c>
+      <c r="HB3">
+        <v>211</v>
+      </c>
+      <c r="HC3">
+        <v>212</v>
+      </c>
+      <c r="HD3">
+        <v>213</v>
+      </c>
+      <c r="HE3">
+        <v>214</v>
+      </c>
+      <c r="HF3">
+        <v>215</v>
+      </c>
+      <c r="HG3">
+        <v>216</v>
+      </c>
+      <c r="HH3">
+        <v>217</v>
+      </c>
+      <c r="HI3">
+        <v>218</v>
+      </c>
+      <c r="HJ3">
+        <v>219</v>
+      </c>
+      <c r="HK3">
+        <v>220</v>
+      </c>
+      <c r="HL3">
+        <v>221</v>
+      </c>
+      <c r="HM3">
+        <v>222</v>
+      </c>
+      <c r="HN3">
+        <v>223</v>
+      </c>
+      <c r="HO3">
+        <v>224</v>
+      </c>
+      <c r="HP3">
+        <v>225</v>
+      </c>
+      <c r="HQ3">
+        <v>226</v>
+      </c>
+      <c r="HR3">
+        <v>227</v>
+      </c>
+      <c r="HS3">
+        <v>228</v>
+      </c>
+      <c r="HT3">
+        <v>229</v>
+      </c>
+      <c r="HU3">
+        <v>230</v>
+      </c>
+      <c r="HV3">
+        <v>231</v>
+      </c>
+      <c r="HW3">
+        <v>232</v>
+      </c>
+      <c r="HX3">
+        <v>233</v>
+      </c>
+      <c r="HY3">
+        <v>234</v>
+      </c>
+      <c r="HZ3">
+        <v>235</v>
+      </c>
+      <c r="IA3">
+        <v>236</v>
+      </c>
+      <c r="IB3">
+        <v>237</v>
+      </c>
+      <c r="IC3">
+        <v>238</v>
+      </c>
+      <c r="ID3">
+        <v>239</v>
+      </c>
+      <c r="IE3">
+        <v>240</v>
+      </c>
+      <c r="IF3">
+        <v>241</v>
+      </c>
+      <c r="IG3">
+        <v>242</v>
+      </c>
+      <c r="IH3">
+        <v>243</v>
+      </c>
+      <c r="II3">
+        <v>244</v>
+      </c>
+      <c r="IJ3">
+        <v>245</v>
+      </c>
+      <c r="IK3">
+        <v>246</v>
+      </c>
+      <c r="IL3">
+        <v>247</v>
+      </c>
+      <c r="IM3">
+        <v>248</v>
+      </c>
+      <c r="IN3">
+        <v>249</v>
+      </c>
+      <c r="IO3">
+        <v>250</v>
+      </c>
+      <c r="IP3">
+        <v>251</v>
+      </c>
+      <c r="IQ3">
+        <v>252</v>
+      </c>
+      <c r="IR3">
+        <v>253</v>
+      </c>
+      <c r="IS3">
+        <v>254</v>
+      </c>
+      <c r="IT3">
+        <v>255</v>
+      </c>
+      <c r="IU3">
+        <v>256</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:255" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>1</v>
       </c>
@@ -692,16 +2938,766 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" t="s">
+        <v>8</v>
+      </c>
+      <c r="I4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" t="s">
+        <v>8</v>
+      </c>
+      <c r="K4" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" t="s">
+        <v>8</v>
+      </c>
+      <c r="N4" t="s">
+        <v>8</v>
+      </c>
+      <c r="O4" t="s">
+        <v>8</v>
+      </c>
+      <c r="P4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>8</v>
+      </c>
+      <c r="R4" t="s">
+        <v>8</v>
+      </c>
+      <c r="S4" t="s">
+        <v>8</v>
+      </c>
+      <c r="T4" t="s">
+        <v>8</v>
+      </c>
+      <c r="U4" t="s">
+        <v>8</v>
+      </c>
+      <c r="V4" t="s">
+        <v>8</v>
+      </c>
+      <c r="W4" t="s">
+        <v>8</v>
+      </c>
+      <c r="X4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AS4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AV4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AY4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BF4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BJ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BL4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BN4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BS4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BW4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BX4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BY4" t="s">
+        <v>8</v>
+      </c>
+      <c r="BZ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CA4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CC4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CD4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CE4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CH4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CI4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CK4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CL4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CM4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CN4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CO4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CP4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CR4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CS4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CT4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CU4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CV4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CW4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CX4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CY4" t="s">
+        <v>8</v>
+      </c>
+      <c r="CZ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DA4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DB4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DC4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DD4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DE4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DF4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DG4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DH4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DI4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DJ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DK4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DL4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DM4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DN4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DO4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DP4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DQ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DR4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DS4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DT4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DU4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DV4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DW4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DX4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DY4" t="s">
+        <v>8</v>
+      </c>
+      <c r="DZ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EA4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EB4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EC4" t="s">
+        <v>8</v>
+      </c>
+      <c r="ED4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EE4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EF4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EG4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EH4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EI4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EJ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EK4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EL4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EM4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EN4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EO4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EP4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EQ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="ER4" t="s">
+        <v>8</v>
+      </c>
+      <c r="ES4" t="s">
+        <v>8</v>
+      </c>
+      <c r="ET4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EU4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EV4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EW4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EX4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EY4" t="s">
+        <v>8</v>
+      </c>
+      <c r="EZ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FA4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FB4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FC4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FD4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FE4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FF4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FG4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FH4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FI4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FJ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FK4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FL4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FM4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FN4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FO4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FP4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FQ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FR4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FS4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FT4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FU4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FV4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FW4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FX4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FY4" t="s">
+        <v>8</v>
+      </c>
+      <c r="FZ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GA4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GB4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GC4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GD4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GE4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GF4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GG4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GH4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GI4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GJ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GK4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GL4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GM4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GN4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GO4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GP4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GQ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GR4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GS4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GT4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GU4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GV4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GW4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GX4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GY4" t="s">
+        <v>8</v>
+      </c>
+      <c r="GZ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HA4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HB4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HC4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HD4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HE4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HF4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HG4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HH4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HI4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HJ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HK4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HL4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HM4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HN4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HO4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HP4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HQ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HR4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HS4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HT4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HU4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HV4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HW4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HX4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HY4" t="s">
+        <v>8</v>
+      </c>
+      <c r="HZ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IA4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IB4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IC4" t="s">
+        <v>8</v>
+      </c>
+      <c r="ID4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IE4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IF4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IG4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IH4" t="s">
+        <v>8</v>
+      </c>
+      <c r="II4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IJ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IK4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IL4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IM4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IN4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IO4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IP4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IQ4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IR4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IS4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IT4" t="s">
+        <v>8</v>
+      </c>
+      <c r="IU4" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:255" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>2</v>
       </c>
@@ -709,16 +3705,766 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" t="s">
+        <v>11</v>
+      </c>
+      <c r="P5" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>11</v>
+      </c>
+      <c r="R5" t="s">
+        <v>11</v>
+      </c>
+      <c r="S5" t="s">
+        <v>11</v>
+      </c>
+      <c r="T5" t="s">
+        <v>11</v>
+      </c>
+      <c r="U5" t="s">
+        <v>11</v>
+      </c>
+      <c r="V5" t="s">
+        <v>11</v>
+      </c>
+      <c r="W5" t="s">
+        <v>11</v>
+      </c>
+      <c r="X5" t="s">
+        <v>11</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>11</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AL5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AQ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AS5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AT5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AU5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AV5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AW5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AX5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AY5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AZ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BB5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BC5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BE5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BF5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BG5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BH5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BI5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BJ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BK5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BL5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BM5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BN5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BP5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BR5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BS5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BW5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BX5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BY5" t="s">
+        <v>11</v>
+      </c>
+      <c r="BZ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CA5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CC5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CD5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CE5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CF5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CG5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CH5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CI5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CJ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CK5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CL5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CM5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CN5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CO5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CP5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CQ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CR5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CS5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CT5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CU5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CV5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CW5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CX5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CY5" t="s">
+        <v>11</v>
+      </c>
+      <c r="CZ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DA5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DB5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DC5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DD5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DE5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DF5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DG5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DH5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DI5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DJ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DK5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DL5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DM5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DN5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DO5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DP5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DQ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DR5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DS5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DT5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DU5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DV5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DW5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DX5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DY5" t="s">
+        <v>11</v>
+      </c>
+      <c r="DZ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EA5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EB5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EC5" t="s">
+        <v>11</v>
+      </c>
+      <c r="ED5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EE5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EF5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EG5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EH5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EI5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EJ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EK5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EL5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EM5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EN5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EO5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EP5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EQ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="ER5" t="s">
+        <v>11</v>
+      </c>
+      <c r="ES5" t="s">
+        <v>11</v>
+      </c>
+      <c r="ET5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EU5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EV5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EW5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EX5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EY5" t="s">
+        <v>11</v>
+      </c>
+      <c r="EZ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FA5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FB5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FC5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FD5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FE5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FF5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FG5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FH5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FI5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FJ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FK5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FL5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FM5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FN5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FO5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FP5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FQ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FR5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FS5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FT5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FU5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FV5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FW5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FX5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FY5" t="s">
+        <v>11</v>
+      </c>
+      <c r="FZ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GA5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GB5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GC5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GD5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GE5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GF5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GG5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GH5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GI5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GJ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GK5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GL5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GM5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GN5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GO5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GP5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GQ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GR5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GS5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GT5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GU5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GV5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GW5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GX5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GY5" t="s">
+        <v>11</v>
+      </c>
+      <c r="GZ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HA5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HB5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HC5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HD5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HE5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HF5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HG5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HH5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HI5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HJ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HK5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HL5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HM5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HN5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HO5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HP5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HQ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HR5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HS5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HT5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HU5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HV5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HW5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HX5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HY5" t="s">
+        <v>11</v>
+      </c>
+      <c r="HZ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IA5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IB5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IC5" t="s">
+        <v>11</v>
+      </c>
+      <c r="ID5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IE5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IF5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IG5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IH5" t="s">
+        <v>11</v>
+      </c>
+      <c r="II5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IJ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IK5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IL5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IM5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IN5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IO5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IP5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IQ5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IR5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IS5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IT5" t="s">
+        <v>11</v>
+      </c>
+      <c r="IU5" t="s">
+        <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:255" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3</v>
       </c>
@@ -726,16 +4472,766 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" t="s">
+        <v>13</v>
+      </c>
+      <c r="L6" t="s">
+        <v>13</v>
+      </c>
+      <c r="M6" t="s">
+        <v>13</v>
+      </c>
+      <c r="N6" t="s">
+        <v>13</v>
+      </c>
+      <c r="O6" t="s">
+        <v>13</v>
+      </c>
+      <c r="P6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>13</v>
+      </c>
+      <c r="R6" t="s">
+        <v>13</v>
+      </c>
+      <c r="S6" t="s">
+        <v>13</v>
+      </c>
+      <c r="T6" t="s">
+        <v>13</v>
+      </c>
+      <c r="U6" t="s">
+        <v>13</v>
+      </c>
+      <c r="V6" t="s">
+        <v>13</v>
+      </c>
+      <c r="W6" t="s">
+        <v>13</v>
+      </c>
+      <c r="X6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AQ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AS6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AT6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AU6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AV6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AW6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AX6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AY6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AZ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BB6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BF6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BH6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BL6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BQ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BR6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BW6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BX6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BY6" t="s">
+        <v>13</v>
+      </c>
+      <c r="BZ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CA6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CC6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CD6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CE6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CF6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CG6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CH6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CI6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CJ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CK6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CL6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CM6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CN6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CO6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CP6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CQ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CR6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CS6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CT6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CU6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CV6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CW6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CX6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CY6" t="s">
+        <v>13</v>
+      </c>
+      <c r="CZ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DA6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DB6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DC6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DD6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DE6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DF6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DG6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DH6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DI6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DJ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DK6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DL6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DM6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DN6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DO6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DP6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DQ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DR6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DS6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DT6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DU6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DV6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DW6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DX6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DY6" t="s">
+        <v>13</v>
+      </c>
+      <c r="DZ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EA6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EB6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EC6" t="s">
+        <v>13</v>
+      </c>
+      <c r="ED6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EE6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EF6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EG6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EH6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EI6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EJ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EK6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EL6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EM6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EN6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EO6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EP6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EQ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="ER6" t="s">
+        <v>13</v>
+      </c>
+      <c r="ES6" t="s">
+        <v>13</v>
+      </c>
+      <c r="ET6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EU6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EV6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EW6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EX6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EY6" t="s">
+        <v>13</v>
+      </c>
+      <c r="EZ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FA6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FB6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FC6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FD6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FE6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FF6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FG6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FH6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FI6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FJ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FK6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FL6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FM6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FN6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FO6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FP6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FQ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FR6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FS6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FT6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FU6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FV6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FW6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FX6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FY6" t="s">
+        <v>13</v>
+      </c>
+      <c r="FZ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GA6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GB6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GC6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GD6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GE6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GF6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GG6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GH6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GI6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GJ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GK6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GL6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GM6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GN6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GO6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GP6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GQ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GR6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GS6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GT6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GU6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GV6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GW6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GX6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GY6" t="s">
+        <v>13</v>
+      </c>
+      <c r="GZ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HA6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HB6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HC6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HD6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HE6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HF6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HG6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HH6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HI6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HJ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HK6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HL6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HM6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HN6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HO6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HP6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HQ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HR6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HS6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HT6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HU6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HV6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HW6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HX6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HY6" t="s">
+        <v>13</v>
+      </c>
+      <c r="HZ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IA6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IB6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IC6" t="s">
+        <v>13</v>
+      </c>
+      <c r="ID6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IE6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IF6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IG6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IH6" t="s">
+        <v>13</v>
+      </c>
+      <c r="II6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IJ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IK6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IL6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IM6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IN6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IO6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IP6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IQ6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IR6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IS6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IT6" t="s">
+        <v>13</v>
+      </c>
+      <c r="IU6" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:255" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>4</v>
       </c>
@@ -743,16 +5239,766 @@
         <v>10</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" t="s">
+        <v>10</v>
+      </c>
+      <c r="K7" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" t="s">
+        <v>10</v>
+      </c>
+      <c r="M7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O7" t="s">
+        <v>10</v>
+      </c>
+      <c r="P7" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>10</v>
+      </c>
+      <c r="R7" t="s">
+        <v>10</v>
+      </c>
+      <c r="S7" t="s">
+        <v>10</v>
+      </c>
+      <c r="T7" t="s">
+        <v>10</v>
+      </c>
+      <c r="U7" t="s">
+        <v>10</v>
+      </c>
+      <c r="V7" t="s">
+        <v>10</v>
+      </c>
+      <c r="W7" t="s">
+        <v>10</v>
+      </c>
+      <c r="X7" t="s">
+        <v>10</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>10</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AG7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AL7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AQ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AS7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AT7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AU7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AV7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AW7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AX7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AY7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AZ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BA7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BB7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BC7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BE7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BF7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BG7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BH7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BI7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BJ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BL7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BM7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BN7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BP7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BR7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BV7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BW7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BX7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BY7" t="s">
+        <v>10</v>
+      </c>
+      <c r="BZ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CA7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CC7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CD7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CE7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CF7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CG7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CH7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CI7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CJ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CK7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CL7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CM7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CN7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CO7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CP7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CQ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CR7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CS7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CT7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CU7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CV7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CW7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CX7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CY7" t="s">
+        <v>10</v>
+      </c>
+      <c r="CZ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DA7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DB7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DC7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DD7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DE7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DF7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DG7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DH7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DI7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DJ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DK7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DL7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DM7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DN7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DO7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DP7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DQ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DR7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DS7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DT7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DU7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DV7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DW7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DX7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DY7" t="s">
+        <v>10</v>
+      </c>
+      <c r="DZ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EA7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EB7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EC7" t="s">
+        <v>10</v>
+      </c>
+      <c r="ED7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EE7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EF7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EG7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EH7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EI7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EJ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EK7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EL7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EM7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EN7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EO7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EP7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EQ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="ER7" t="s">
+        <v>10</v>
+      </c>
+      <c r="ES7" t="s">
+        <v>10</v>
+      </c>
+      <c r="ET7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EU7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EV7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EW7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EX7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EY7" t="s">
+        <v>10</v>
+      </c>
+      <c r="EZ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FA7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FB7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FC7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FD7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FE7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FF7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FG7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FH7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FI7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FJ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FK7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FL7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FM7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FN7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FO7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FP7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FQ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FR7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FS7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FT7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FU7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FV7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FW7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FX7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FY7" t="s">
+        <v>10</v>
+      </c>
+      <c r="FZ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GA7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GB7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GC7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GD7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GE7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GF7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GG7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GH7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GI7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GJ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GK7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GL7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GM7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GN7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GO7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GP7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GQ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GR7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GS7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GT7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GU7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GV7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GW7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GX7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GY7" t="s">
+        <v>10</v>
+      </c>
+      <c r="GZ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HA7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HB7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HC7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HD7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HE7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HF7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HG7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HH7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HI7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HJ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HK7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HL7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HM7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HN7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HO7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HP7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HQ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HR7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HS7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HT7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HU7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HV7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HW7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HX7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HY7" t="s">
+        <v>10</v>
+      </c>
+      <c r="HZ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IA7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IB7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IC7" t="s">
+        <v>10</v>
+      </c>
+      <c r="ID7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IE7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IF7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IG7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IH7" t="s">
+        <v>10</v>
+      </c>
+      <c r="II7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IJ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IK7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IL7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IM7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IN7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IO7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IP7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IQ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IR7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IS7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IT7" t="s">
+        <v>10</v>
+      </c>
+      <c r="IU7" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:255" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -760,16 +6006,766 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M8" t="s">
+        <v>14</v>
+      </c>
+      <c r="N8" t="s">
+        <v>14</v>
+      </c>
+      <c r="O8" t="s">
+        <v>14</v>
+      </c>
+      <c r="P8" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>14</v>
+      </c>
+      <c r="R8" t="s">
+        <v>14</v>
+      </c>
+      <c r="S8" t="s">
+        <v>14</v>
+      </c>
+      <c r="T8" t="s">
+        <v>14</v>
+      </c>
+      <c r="U8" t="s">
+        <v>14</v>
+      </c>
+      <c r="V8" t="s">
+        <v>14</v>
+      </c>
+      <c r="W8" t="s">
+        <v>14</v>
+      </c>
+      <c r="X8" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AY8" t="s">
+        <v>14</v>
+      </c>
+      <c r="AZ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BA8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BB8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BC8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BE8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BF8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BG8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BH8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BI8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BJ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BK8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BL8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BM8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BN8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BO8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BP8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BQ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BR8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BV8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BW8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BX8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BY8" t="s">
+        <v>14</v>
+      </c>
+      <c r="BZ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CA8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CC8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CD8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CE8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CF8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CG8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CH8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CI8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CJ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CK8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CL8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CM8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CN8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CO8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CP8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CQ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CR8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CS8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CT8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CU8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CV8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CW8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CX8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CY8" t="s">
+        <v>14</v>
+      </c>
+      <c r="CZ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DA8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DB8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DC8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DD8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DE8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DF8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DG8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DH8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DI8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DJ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DK8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DL8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DM8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DN8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DO8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DP8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DQ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DR8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DS8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DT8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DU8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DV8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DW8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DX8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DY8" t="s">
+        <v>14</v>
+      </c>
+      <c r="DZ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EA8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EB8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EC8" t="s">
+        <v>14</v>
+      </c>
+      <c r="ED8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EE8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EF8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EG8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EH8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EI8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EJ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EK8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EL8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EM8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EN8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EO8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EP8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EQ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="ER8" t="s">
+        <v>14</v>
+      </c>
+      <c r="ES8" t="s">
+        <v>14</v>
+      </c>
+      <c r="ET8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EU8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EV8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EW8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EX8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EY8" t="s">
+        <v>14</v>
+      </c>
+      <c r="EZ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FA8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FB8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FC8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FD8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FE8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FF8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FG8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FH8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FI8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FJ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FK8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FL8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FM8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FN8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FO8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FP8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FQ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FR8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FS8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FT8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FU8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FV8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FW8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FX8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FY8" t="s">
+        <v>14</v>
+      </c>
+      <c r="FZ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GA8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GB8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GC8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GD8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GE8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GF8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GG8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GH8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GI8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GJ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GK8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GL8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GM8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GN8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GO8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GP8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GQ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GR8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GS8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GT8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GU8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GV8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GW8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GX8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GY8" t="s">
+        <v>14</v>
+      </c>
+      <c r="GZ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HA8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HB8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HC8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HD8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HE8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HF8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HG8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HH8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HI8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HJ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HK8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HL8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HM8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HN8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HO8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HP8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HQ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HR8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HS8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HT8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HU8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HV8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HW8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HX8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HY8" t="s">
+        <v>14</v>
+      </c>
+      <c r="HZ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IA8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IB8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IC8" t="s">
+        <v>14</v>
+      </c>
+      <c r="ID8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IE8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IF8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IG8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IH8" t="s">
+        <v>14</v>
+      </c>
+      <c r="II8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IJ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IK8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IL8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IM8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IN8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IO8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IP8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IQ8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IR8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IS8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IT8" t="s">
+        <v>14</v>
+      </c>
+      <c r="IU8" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:255" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>6</v>
       </c>
@@ -777,16 +6773,766 @@
         <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s">
+        <v>15</v>
+      </c>
+      <c r="K9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" t="s">
+        <v>15</v>
+      </c>
+      <c r="N9" t="s">
+        <v>15</v>
+      </c>
+      <c r="O9" t="s">
+        <v>15</v>
+      </c>
+      <c r="P9" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>15</v>
+      </c>
+      <c r="R9" t="s">
+        <v>15</v>
+      </c>
+      <c r="S9" t="s">
+        <v>15</v>
+      </c>
+      <c r="T9" t="s">
+        <v>15</v>
+      </c>
+      <c r="U9" t="s">
+        <v>15</v>
+      </c>
+      <c r="V9" t="s">
+        <v>15</v>
+      </c>
+      <c r="W9" t="s">
+        <v>15</v>
+      </c>
+      <c r="X9" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AY9" t="s">
+        <v>15</v>
+      </c>
+      <c r="AZ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BA9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BB9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BC9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BE9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BF9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BG9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BH9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BI9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BJ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BK9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BL9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BM9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BN9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BO9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BP9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BQ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BR9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BS9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BV9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BW9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BX9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BY9" t="s">
+        <v>15</v>
+      </c>
+      <c r="BZ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CA9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CC9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CD9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CE9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CF9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CG9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CH9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CI9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CJ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CK9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CL9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CM9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CN9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CO9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CP9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CQ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CR9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CS9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CT9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CU9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CV9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CW9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CX9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CY9" t="s">
+        <v>15</v>
+      </c>
+      <c r="CZ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DA9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DB9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DC9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DD9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DE9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DF9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DG9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DH9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DI9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DJ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DK9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DL9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DM9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DN9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DO9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DP9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DQ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DR9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DS9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DT9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DU9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DV9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DW9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DX9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DY9" t="s">
+        <v>15</v>
+      </c>
+      <c r="DZ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EA9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EB9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EC9" t="s">
+        <v>15</v>
+      </c>
+      <c r="ED9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EE9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EF9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EG9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EH9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EI9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EJ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EK9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EL9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EM9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EN9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EO9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EP9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EQ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="ER9" t="s">
+        <v>15</v>
+      </c>
+      <c r="ES9" t="s">
+        <v>15</v>
+      </c>
+      <c r="ET9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EU9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EV9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EW9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EX9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EY9" t="s">
+        <v>15</v>
+      </c>
+      <c r="EZ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FA9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FB9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FC9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FD9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FE9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FF9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FG9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FH9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FI9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FJ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FK9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FL9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FM9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FN9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FO9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FP9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FQ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FR9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FS9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FT9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FU9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FV9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FW9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FX9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FY9" t="s">
+        <v>15</v>
+      </c>
+      <c r="FZ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GA9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GB9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GC9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GD9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GE9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GF9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GG9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GH9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GI9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GJ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GK9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GL9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GM9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GN9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GO9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GP9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GQ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GR9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GS9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GT9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GU9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GV9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GW9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GX9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GY9" t="s">
+        <v>15</v>
+      </c>
+      <c r="GZ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HA9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HB9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HC9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HD9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HE9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HF9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HG9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HH9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HI9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HJ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HK9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HL9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HM9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HN9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HO9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HP9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HQ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HR9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HS9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HT9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HU9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HV9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HW9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HX9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HY9" t="s">
+        <v>15</v>
+      </c>
+      <c r="HZ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IA9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IB9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IC9" t="s">
+        <v>15</v>
+      </c>
+      <c r="ID9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IE9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IF9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IG9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IH9" t="s">
+        <v>15</v>
+      </c>
+      <c r="II9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IJ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IK9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IL9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IM9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IN9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IO9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IP9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IQ9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IR9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IS9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IT9" t="s">
+        <v>15</v>
+      </c>
+      <c r="IU9" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:255" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>7</v>
       </c>
@@ -794,16 +7540,766 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>9</v>
+      </c>
+      <c r="I10" t="s">
+        <v>9</v>
+      </c>
+      <c r="J10" t="s">
+        <v>9</v>
+      </c>
+      <c r="K10" t="s">
+        <v>9</v>
+      </c>
+      <c r="L10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M10" t="s">
+        <v>9</v>
+      </c>
+      <c r="N10" t="s">
+        <v>9</v>
+      </c>
+      <c r="O10" t="s">
+        <v>9</v>
+      </c>
+      <c r="P10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>9</v>
+      </c>
+      <c r="R10" t="s">
+        <v>9</v>
+      </c>
+      <c r="S10" t="s">
+        <v>9</v>
+      </c>
+      <c r="T10" t="s">
+        <v>9</v>
+      </c>
+      <c r="U10" t="s">
+        <v>9</v>
+      </c>
+      <c r="V10" t="s">
+        <v>9</v>
+      </c>
+      <c r="W10" t="s">
+        <v>9</v>
+      </c>
+      <c r="X10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>9</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AG10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AH10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AN10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AT10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AV10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AY10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AZ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BA10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BB10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BC10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BE10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BF10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BG10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BH10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BI10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BJ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BK10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BL10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BM10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BN10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BO10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BP10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BQ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BR10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BS10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BV10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BW10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BX10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BY10" t="s">
+        <v>9</v>
+      </c>
+      <c r="BZ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CA10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CC10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CD10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CE10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CF10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CG10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CH10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CI10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CJ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CK10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CL10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CM10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CN10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CO10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CP10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CQ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CR10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CS10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CT10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CU10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CV10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CW10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CX10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CY10" t="s">
+        <v>9</v>
+      </c>
+      <c r="CZ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DA10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DB10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DC10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DD10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DE10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DF10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DG10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DH10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DI10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DJ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DK10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DL10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DM10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DN10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DO10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DP10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DQ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DR10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DS10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DT10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DU10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DV10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DW10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DX10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DY10" t="s">
+        <v>9</v>
+      </c>
+      <c r="DZ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EA10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EB10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EC10" t="s">
+        <v>9</v>
+      </c>
+      <c r="ED10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EE10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EF10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EG10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EH10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EI10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EJ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EK10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EL10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EM10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EN10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EO10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EP10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EQ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="ER10" t="s">
+        <v>9</v>
+      </c>
+      <c r="ES10" t="s">
+        <v>9</v>
+      </c>
+      <c r="ET10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EU10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EV10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EW10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EX10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EY10" t="s">
+        <v>9</v>
+      </c>
+      <c r="EZ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FA10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FB10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FC10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FD10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FE10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FF10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FG10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FH10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FI10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FJ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FK10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FL10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FM10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FN10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FO10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FP10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FQ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FR10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FS10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FT10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FU10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FV10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FW10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FX10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FY10" t="s">
+        <v>9</v>
+      </c>
+      <c r="FZ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GA10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GB10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GC10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GD10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GE10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GF10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GG10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GH10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GI10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GJ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GK10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GL10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GM10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GN10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GO10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GP10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GQ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GR10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GS10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GT10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GU10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GV10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GW10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GX10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GY10" t="s">
+        <v>9</v>
+      </c>
+      <c r="GZ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HA10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HB10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HC10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HD10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HE10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HF10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HG10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HH10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HI10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HJ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HK10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HL10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HM10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HN10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HO10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HP10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HQ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HR10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HS10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HT10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HU10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HV10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HW10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HX10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HY10" t="s">
+        <v>9</v>
+      </c>
+      <c r="HZ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IA10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IB10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IC10" t="s">
+        <v>9</v>
+      </c>
+      <c r="ID10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IE10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IF10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IG10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IH10" t="s">
+        <v>9</v>
+      </c>
+      <c r="II10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IJ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IK10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IL10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IM10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IN10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IO10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IP10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IQ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IR10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IS10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IT10" t="s">
+        <v>9</v>
+      </c>
+      <c r="IU10" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:255" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>8</v>
       </c>
@@ -811,16 +8307,766 @@
         <v>12</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>12</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" t="s">
+        <v>12</v>
+      </c>
+      <c r="K11" t="s">
+        <v>12</v>
+      </c>
+      <c r="L11" t="s">
+        <v>12</v>
+      </c>
+      <c r="M11" t="s">
+        <v>12</v>
+      </c>
+      <c r="N11" t="s">
+        <v>12</v>
+      </c>
+      <c r="O11" t="s">
+        <v>12</v>
+      </c>
+      <c r="P11" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>12</v>
+      </c>
+      <c r="R11" t="s">
+        <v>12</v>
+      </c>
+      <c r="S11" t="s">
+        <v>12</v>
+      </c>
+      <c r="T11" t="s">
+        <v>12</v>
+      </c>
+      <c r="U11" t="s">
+        <v>12</v>
+      </c>
+      <c r="V11" t="s">
+        <v>12</v>
+      </c>
+      <c r="W11" t="s">
+        <v>12</v>
+      </c>
+      <c r="X11" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AN11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AO11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AQ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AS11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AT11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AV11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AY11" t="s">
+        <v>12</v>
+      </c>
+      <c r="AZ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BA11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BB11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BC11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BE11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BF11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BG11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BH11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BI11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BJ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BK11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BL11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BM11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BN11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BO11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BP11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BQ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BR11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BS11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BT11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BU11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BV11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BW11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BX11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BY11" t="s">
+        <v>12</v>
+      </c>
+      <c r="BZ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CA11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CC11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CD11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CE11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CF11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CG11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CH11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CI11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CJ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CK11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CL11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CM11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CN11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CO11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CP11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CQ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CR11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CS11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CT11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CU11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CV11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CW11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CX11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CY11" t="s">
+        <v>12</v>
+      </c>
+      <c r="CZ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DA11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DB11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DC11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DD11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DE11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DF11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DG11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DH11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DI11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DJ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DK11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DL11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DM11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DN11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DO11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DP11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DQ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DR11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DS11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DT11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DU11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DV11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DW11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DX11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DY11" t="s">
+        <v>12</v>
+      </c>
+      <c r="DZ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EA11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EB11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EC11" t="s">
+        <v>12</v>
+      </c>
+      <c r="ED11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EE11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EF11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EG11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EH11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EI11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EJ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EK11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EL11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EM11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EN11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EO11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EP11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EQ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="ER11" t="s">
+        <v>12</v>
+      </c>
+      <c r="ES11" t="s">
+        <v>12</v>
+      </c>
+      <c r="ET11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EU11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EV11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EW11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EX11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EY11" t="s">
+        <v>12</v>
+      </c>
+      <c r="EZ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FA11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FB11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FC11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FD11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FE11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FF11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FG11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FH11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FI11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FJ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FK11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FL11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FM11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FN11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FO11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FP11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FQ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FR11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FS11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FT11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FU11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FV11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FW11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FX11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FY11" t="s">
+        <v>12</v>
+      </c>
+      <c r="FZ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GA11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GB11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GC11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GD11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GE11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GF11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GG11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GH11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GI11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GJ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GK11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GL11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GM11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GN11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GO11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GP11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GQ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GR11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GS11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GT11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GU11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GV11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GW11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GX11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GY11" t="s">
+        <v>12</v>
+      </c>
+      <c r="GZ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HA11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HB11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HC11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HD11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HE11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HF11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HG11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HH11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HI11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HJ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HK11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HL11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HM11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HN11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HO11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HP11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HQ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HR11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HS11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HT11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HU11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HV11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HW11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HX11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HY11" t="s">
+        <v>12</v>
+      </c>
+      <c r="HZ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IA11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IB11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IC11" t="s">
+        <v>12</v>
+      </c>
+      <c r="ID11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IE11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IF11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IG11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IH11" t="s">
+        <v>12</v>
+      </c>
+      <c r="II11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IJ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IK11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IL11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IM11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IN11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IO11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IP11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IQ11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IR11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IS11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IT11" t="s">
+        <v>12</v>
+      </c>
+      <c r="IU11" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:255" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
@@ -828,13 +9074,763 @@
         <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D12" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>16</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L12" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" t="s">
+        <v>16</v>
+      </c>
+      <c r="N12" t="s">
+        <v>16</v>
+      </c>
+      <c r="O12" t="s">
+        <v>16</v>
+      </c>
+      <c r="P12" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>16</v>
+      </c>
+      <c r="R12" t="s">
+        <v>16</v>
+      </c>
+      <c r="S12" t="s">
+        <v>16</v>
+      </c>
+      <c r="T12" t="s">
+        <v>16</v>
+      </c>
+      <c r="U12" t="s">
+        <v>16</v>
+      </c>
+      <c r="V12" t="s">
+        <v>16</v>
+      </c>
+      <c r="W12" t="s">
+        <v>16</v>
+      </c>
+      <c r="X12" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AT12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AV12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AY12" t="s">
+        <v>16</v>
+      </c>
+      <c r="AZ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BA12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BB12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BC12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BD12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BE12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BF12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BG12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BH12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BI12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BJ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BK12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BL12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BM12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BN12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BO12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BP12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BQ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BR12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BS12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BT12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BU12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BV12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BW12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BX12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BY12" t="s">
+        <v>16</v>
+      </c>
+      <c r="BZ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CA12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CC12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CD12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CE12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CF12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CG12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CH12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CI12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CJ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CK12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CL12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CM12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CN12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CO12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CP12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CQ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CR12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CS12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CT12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CU12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CV12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CW12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CX12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CY12" t="s">
+        <v>16</v>
+      </c>
+      <c r="CZ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DA12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DB12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DC12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DD12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DE12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DF12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DG12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DH12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DI12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DJ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DK12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DL12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DM12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DN12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DO12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DP12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DQ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DR12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DS12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DT12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DU12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DV12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DW12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DX12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DY12" t="s">
+        <v>16</v>
+      </c>
+      <c r="DZ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EA12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EB12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EC12" t="s">
+        <v>16</v>
+      </c>
+      <c r="ED12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EE12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EF12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EG12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EH12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EI12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EJ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EK12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EL12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EM12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EN12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EO12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EP12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EQ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="ER12" t="s">
+        <v>16</v>
+      </c>
+      <c r="ES12" t="s">
+        <v>16</v>
+      </c>
+      <c r="ET12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EU12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EV12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EW12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EX12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EY12" t="s">
+        <v>16</v>
+      </c>
+      <c r="EZ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FA12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FB12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FC12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FD12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FE12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FF12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FG12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FH12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FI12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FJ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FK12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FL12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FM12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FN12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FO12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FP12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FQ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FR12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FS12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FT12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FU12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FV12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FW12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FX12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FY12" t="s">
+        <v>16</v>
+      </c>
+      <c r="FZ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GA12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GB12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GC12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GD12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GE12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GF12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GG12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GH12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GI12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GJ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GK12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GL12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GM12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GN12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GO12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GP12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GQ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GR12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GS12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GT12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GU12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GV12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GW12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GX12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GY12" t="s">
+        <v>16</v>
+      </c>
+      <c r="GZ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HA12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HB12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HC12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HD12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HE12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HF12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HG12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HH12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HI12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HJ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HK12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HL12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HM12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HN12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HO12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HP12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HQ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HR12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HS12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HT12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HU12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HV12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HW12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HX12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HY12" t="s">
+        <v>16</v>
+      </c>
+      <c r="HZ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IA12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IB12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IC12" t="s">
+        <v>16</v>
+      </c>
+      <c r="ID12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IE12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IF12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IG12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IH12" t="s">
+        <v>16</v>
+      </c>
+      <c r="II12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IJ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IK12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IL12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IM12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IN12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IO12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IP12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IQ12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IR12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IS12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IT12" t="s">
+        <v>16</v>
+      </c>
+      <c r="IU12" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
